--- a/artfynd/A 39323-2022 artfynd.xlsx
+++ b/artfynd/A 39323-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124338191</v>
+        <v>124340897</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>58055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375793</v>
+        <v>375585</v>
       </c>
       <c r="R2" t="n">
-        <v>6388632</v>
+        <v>6388549</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,17 +757,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Två mindre högar på hällmark.</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124340897</v>
+        <v>124338191</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,33 +815,29 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +847,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375585</v>
+        <v>375793</v>
       </c>
       <c r="R3" t="n">
-        <v>6388549</v>
+        <v>6388632</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +877,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Två mindre högar på hällmark.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 39323-2022 artfynd.xlsx
+++ b/artfynd/A 39323-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124340897</v>
+        <v>124338191</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
+        <v>56722</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375585</v>
+        <v>375793</v>
       </c>
       <c r="R2" t="n">
-        <v>6388549</v>
+        <v>6388632</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +753,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Två mindre högar på hällmark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124338191</v>
+        <v>124340897</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>58055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,29 +806,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -847,13 +842,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375793</v>
+        <v>375585</v>
       </c>
       <c r="R3" t="n">
-        <v>6388632</v>
+        <v>6388549</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,17 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Två mindre högar på hällmark.</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 39323-2022 artfynd.xlsx
+++ b/artfynd/A 39323-2022 artfynd.xlsx
@@ -802,12 +802,7 @@
         <v>124338191</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39323-2022 artfynd.xlsx
+++ b/artfynd/A 39323-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>124338191</v>
       </c>
       <c r="B3" t="n">
-        <v>57044</v>
+        <v>57052</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39323-2022 artfynd.xlsx
+++ b/artfynd/A 39323-2022 artfynd.xlsx
@@ -802,7 +802,7 @@
         <v>124338191</v>
       </c>
       <c r="B3" t="n">
-        <v>57052</v>
+        <v>57053</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 39323-2022 artfynd.xlsx
+++ b/artfynd/A 39323-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124340897</v>
+        <v>124338191</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,33 +686,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>375585</v>
+        <v>375793</v>
       </c>
       <c r="R2" t="n">
-        <v>6388549</v>
+        <v>6388632</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,22 +748,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:00</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Två mindre högar på hällmark.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,40 +785,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124338191</v>
+        <v>124340897</v>
       </c>
       <c r="B3" t="n">
-        <v>57073</v>
+        <v>58497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +832,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>375793</v>
+        <v>375585</v>
       </c>
       <c r="R3" t="n">
-        <v>6388632</v>
+        <v>6388549</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,17 +862,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Två mindre högar på hällmark.</t>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 39323-2022 artfynd.xlsx
+++ b/artfynd/A 39323-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124338191</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,8 +911,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124340897</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>